--- a/data/partner_data_forLCA/Inventory eelgrass.xlsx
+++ b/data/partner_data_forLCA/Inventory eelgrass.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ngau\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leidenuniv1-my.sharepoint.com/personal/tsuitpy_vuw_leidenuniv_nl/Documents/01_Projects/RAW/lca_for_adaptive_factories/data/partner_data_forLCA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67511A56-F302-44D5-A61D-71C5FB01259E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{67511A56-F302-44D5-A61D-71C5FB01259E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94964132-E32B-1C41-B37C-731F6D800E62}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1940" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Loose Ealgrass" sheetId="8" r:id="rId1"/>
@@ -632,27 +632,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAD441BC-A918-4C24-8E4F-FA2615904A86}">
   <dimension ref="A1:N50"/>
-  <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.08984375" customWidth="1"/>
-    <col min="2" max="2" width="27.36328125" customWidth="1"/>
-    <col min="3" max="3" width="21.7265625" customWidth="1"/>
-    <col min="4" max="4" width="29.36328125" customWidth="1"/>
-    <col min="5" max="5" width="24.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.36328125" customWidth="1"/>
-    <col min="7" max="7" width="9.08984375" customWidth="1"/>
-    <col min="9" max="9" width="31.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" customWidth="1"/>
+    <col min="1" max="1" width="57.1640625" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" customWidth="1"/>
+    <col min="9" max="9" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
     <col min="15" max="15" width="27" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -692,7 +692,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -721,7 +721,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -747,7 +747,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -773,7 +773,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -793,7 +793,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
@@ -813,7 +813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>42</v>
       </c>
@@ -821,7 +821,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="11">
-        <v>0.66060000000000008</v>
+        <v>0.66059999999999997</v>
       </c>
       <c r="I9" t="s">
         <v>7</v>
@@ -830,7 +830,7 @@
         <v>198.18</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>48</v>
       </c>
@@ -838,16 +838,16 @@
         <v>12</v>
       </c>
       <c r="C10" s="11">
-        <v>1.3000000000000001E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="I10" t="s">
         <v>9</v>
       </c>
       <c r="J10" s="9">
-        <v>3.9000000000000004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>49</v>
       </c>
@@ -864,7 +864,7 @@
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>50</v>
       </c>
@@ -881,7 +881,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -901,7 +901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="I14" t="s">
         <v>7</v>
       </c>
@@ -909,7 +909,7 @@
         <v>66.06</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>16</v>
       </c>
@@ -922,7 +922,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -943,7 +943,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -964,14 +964,14 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>24</v>
       </c>
@@ -982,7 +982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -997,14 +997,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>31</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="13" t="s">
         <v>28</v>
       </c>
@@ -1034,7 +1034,7 @@
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>31</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C43" t="s">
         <v>34</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C44" t="s">
         <v>35</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C45" t="s">
         <v>36</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C46" t="s">
         <v>37</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
         <v>38</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C48" t="s">
         <v>22</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="50" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F50" t="s">
         <v>39</v>
       </c>
@@ -1182,6 +1182,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e035afa5-203b-4855-b0e0-7c5ecaec1505">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="021125cc-83eb-463c-a69b-38079fd148ea" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1190,7 +1201,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010072D0A9AA16B8AA4CBBD6AE36636EA318" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="97bc0a5f1a727efdd5997cd14b817678">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e035afa5-203b-4855-b0e0-7c5ecaec1505" xmlns:ns3="021125cc-83eb-463c-a69b-38079fd148ea" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d413dacdc01c41041bc6ab826c0e56c7" ns2:_="" ns3:_="">
     <xsd:import namespace="e035afa5-203b-4855-b0e0-7c5ecaec1505"/>
@@ -1431,18 +1442,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e035afa5-203b-4855-b0e0-7c5ecaec1505">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="021125cc-83eb-463c-a69b-38079fd148ea" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ECD0532-8DE0-439C-9100-68A6B0503475}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="e035afa5-203b-4855-b0e0-7c5ecaec1505"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="021125cc-83eb-463c-a69b-38079fd148ea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FDC4376-33A1-40E3-8FAD-FBBD374D4E92}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -1450,7 +1467,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8250828-151D-4CC1-A818-3B2CBAC8FFEB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1469,19 +1486,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ECD0532-8DE0-439C-9100-68A6B0503475}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="021125cc-83eb-463c-a69b-38079fd148ea"/>
-    <ds:schemaRef ds:uri="e035afa5-203b-4855-b0e0-7c5ecaec1505"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d465f887-04a9-4c17-8b62-103eddccf68b}" enabled="1" method="Standard" siteId="{ca2a7f76-dbd7-4ec0-9108-6b3d524fb7c8}" removed="0"/>
+</clbl:labelList>
 </file>